--- a/artfynd/A 62483-2021 artfynd.xlsx
+++ b/artfynd/A 62483-2021 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>115147146</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 62483-2021 artfynd.xlsx
+++ b/artfynd/A 62483-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115147136</v>
+        <v>115268207</v>
       </c>
       <c r="B2" t="n">
-        <v>57215</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102621</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,14 +705,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508064</v>
+        <v>508131</v>
       </c>
       <c r="R2" t="n">
-        <v>6398434</v>
+        <v>6398467</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115147135</v>
+        <v>115147138</v>
       </c>
       <c r="B3" t="n">
-        <v>56611</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -923,32 +913,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115147138</v>
+        <v>115147135</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1047,15 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115147146</v>
+        <v>115268214</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,16 +1043,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>100065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,14 +1062,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1099,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508064</v>
+        <v>508131</v>
       </c>
       <c r="R5" t="n">
-        <v>6398434</v>
+        <v>6398467</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,6 +1148,1549 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115268218</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115268225</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58067</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115268211</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115147136</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>508064</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6398434</v>
+      </c>
+      <c r="S9" t="n">
+        <v>12</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115268221</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115268216</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57364</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>115147146</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>508064</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6398434</v>
+      </c>
+      <c r="S12" t="n">
+        <v>12</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115268235</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115268229</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115268239</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115268244</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115268247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>115268227</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Boaryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6398467</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62483-2021 artfynd.xlsx
+++ b/artfynd/A 62483-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268207</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115147138</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115147135</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268214</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1271,6 +1296,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268218</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1390,6 +1420,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268225</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1509,6 +1544,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268211</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1628,6 +1668,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115147136</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1747,6 +1792,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268221</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1866,6 +1916,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268216</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1985,6 +2040,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115147146</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2104,6 +2164,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268235</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2223,6 +2288,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268229</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2338,6 +2408,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268239</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2457,6 +2532,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268244</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2576,6 +2656,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268247</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2691,8 +2776,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268227</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>